--- a/www/download/COUNTRY.ROW.zdW13.xlsx
+++ b/www/download/COUNTRY.ROW.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Resto do mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,12 +852,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -934,2436 +939,3997 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>856.406</t>
+          <t>-0.617401796089394</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>877.09</t>
+          <t>-0.588920461797345</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>896.559</t>
+          <t>-0.585013268959882</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>911.591</t>
+          <t>-0.593006362370251</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>926.097</t>
+          <t>-0.604652697230394</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>955.308</t>
+          <t>-0.601676588556694</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>983.772</t>
+          <t>-0.584259736512084</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>998.606</t>
+          <t>-0.587244789412835</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1035.462</t>
+          <t>-0.555043573549589</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1066.542</t>
+          <t>-0.52487497870046</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1095.297</t>
+          <t>-0.52854004245487</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1124.55</t>
+          <t>-0.523612040494736</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1146.413</t>
+          <t>-0.470634148761849</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1174.341</t>
+          <t>-0.438810075381364</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1192.928</t>
+          <t>-0.438799369490669</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>370.557</t>
+          <t>-0.0127987350070456</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>379.509</t>
+          <t>0.0594430859371158</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>390.19</t>
+          <t>0.0643526177232556</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>395.691</t>
+          <t>0.0613626085826744</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>400.131</t>
+          <t>0.0602976204637673</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>413.204</t>
+          <t>0.0483124482342006</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>426.421</t>
+          <t>0.0595764049972289</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>433.848</t>
+          <t>0.0800131939530786</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>450.765</t>
+          <t>0.15594300398153</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>467.784</t>
+          <t>0.225056485363291</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>483.061</t>
+          <t>0.222298651750885</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>500.543</t>
+          <t>0.227249422941632</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>514.72</t>
+          <t>0.33409627720114</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>530.955</t>
+          <t>0.36556176417692</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>0.416312911983843</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>1.15576654678628</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>1.2784595018725</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>1.32944786041268</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>1.39611467935391</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>1.43085564245665</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>1.34689465660397</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>1.40346228569705</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>1.47462063062402</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>1.25886136336434</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>1.66186700853734</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>1.59340604570912</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>1.54986512599455</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>1.60352527139558</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>1.51614614455436</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>1.77449574672923</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>738866.487</t>
+          <t>2050739765956.09</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>776405.09</t>
+          <t>2097344067954.26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>798568.775</t>
+          <t>2138286852430.43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>803407.524</t>
+          <t>2174711948457.64</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>822249.294</t>
+          <t>2183529099155.79</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>855199.877</t>
+          <t>2257224744292.89</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>891213.742</t>
+          <t>2343784885980.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>900784.444</t>
+          <t>2421717544261.65</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>941392</t>
+          <t>2524777868950.96</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>994182.907</t>
+          <t>2609861024313.3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1014205.444</t>
+          <t>2675242693495.76</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1047826.004</t>
+          <t>2799468074300.45</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1087701.752</t>
+          <t>2805198530696.85</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1141488.884</t>
+          <t>2879624772911.33</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1160918.34</t>
+          <t>2965900033982.57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>689507835948.644</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>686651772655.516</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>704610494143.487</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>711330793805.077</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>738082053073.131</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>785794355894.522</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>810353259521.882</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>812769769240.058</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>827798036124.983</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>825469701695.088</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>854710247981.291</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>886644891817.58</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>864274693872.998</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>895264433509.561</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>893184792087.304</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>7667082.56815636</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>7567208.77237378</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>7597599.8256853</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.56</t>
+          <t>8019840.00449013</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>8090189.80258283</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>8255191.56342051</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>8762585.00997788</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>8758129.13102928</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>8398985.08536099</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>7823398.04182931</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>47.03</t>
+          <t>7101867.06425462</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>6510479.8558474</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>5712654.30426432</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>4937908.911404</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>5419239.85193627</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>11625293.8467547</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>11949684.1081556</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.39</t>
+          <t>12109226.8824011</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>12155335.5988199</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>12849095.7108573</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>13582748.2125991</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>13623494.3588201</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>14368869.4188734</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>16052951.6365496</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>18168549.7184322</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>19873893.5679743</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>21530437.893548</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24492854.1643649</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>27630206.5178216</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>26082562.9010511</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>17670134.7640659</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>18201052.3175418</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>18496826.3407095</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>18622144.9045018</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.47</t>
+          <t>19448642.3096824</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>20437511.9239148</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>20609654.757445</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>21759786.6316304</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>24319993.405608</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>27651335.632265</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>30358138.7082923</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>33164418.43728</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>37444154.8822197</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>42082096.3532651</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>40404332.280805</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>0.071585337751725</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>0.130711549371719</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>0.13334783120386</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>0.129442913175889</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>0.114035073704453</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>0.0883252987862739</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>0.0997842379795852</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>0.108289798521977</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>0.137224249297189</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>0.204384491380075</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.186607328240815</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>0.181787673116957</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>0.258513942299327</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.275029858079926</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>0.299751575047654</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1860.73595164121</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1809.31511897092</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1805.8129084476</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1797.69246401941</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1844.6027587306</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1901.70924133158</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1900.35894790131</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1873.39940408129</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1836.42846236533</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1764.63705706054</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1769.36115388259</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1771.36445351957</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1679.11754704009</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1686.14053162624</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1652.09480290201</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.656</t>
+          <t>-232745397522.007</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.752</t>
+          <t>-241033306652.853</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>-201307694534.391</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.711</t>
+          <t>-218372405261.616</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>-232574886929.702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>-254966280842.994</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>-271045433460.653</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>-282375023668.331</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>-325461861556.649</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.269</t>
+          <t>-352857766182.94</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>-349479805758.797</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.975</t>
+          <t>-354834234057.555</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.462</t>
+          <t>-368709565758.066</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-386530671323.065</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-371226049853.206</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.913</t>
+          <t>-215118879725.083</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>-222573786048.106</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>-180306037707.546</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>-197499307002.697</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>-210857340519.522</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>-228988180209.059</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>-246994463900.473</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>-253841716884.454</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>-295130827982.93</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>-317517245252.885</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.963</t>
+          <t>-311183682149.626</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>-313765187664.258</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.944</t>
+          <t>-325539635281.607</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>-347428713330.267</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>-337297362755.627</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11.287</t>
+          <t>-17626517796.9239</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>11.943</t>
+          <t>-18459520604.7465</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.946</t>
+          <t>-21001656826.8445</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11.365</t>
+          <t>-20873098258.9192</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11.408</t>
+          <t>-21717546410.1799</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11.324</t>
+          <t>-25978100633.9347</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.035</t>
+          <t>-24050969560.1801</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.701</t>
+          <t>-28533306783.8766</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>11.762</t>
+          <t>-30331033573.7192</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>13.123</t>
+          <t>-35340520930.0549</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.756</t>
+          <t>-38296123609.1705</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16.116</t>
+          <t>-41069046393.2966</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>18.165</t>
+          <t>-43169930476.4591</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>16.479</t>
+          <t>-39101957992.7973</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>-33928687097.5783</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6.003</t>
+          <t>1993.93736320623</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.424</t>
+          <t>2045.81350147328</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>2046.61414334903</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.264</t>
+          <t>2030.39101355642</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.334</t>
+          <t>2054.95217027789</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6.598</t>
+          <t>2069.67827827681</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.586</t>
+          <t>2089.98481740532</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.544</t>
+          <t>2076.26944810044</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>2088.4309795014</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>2125.30150443829</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.019</t>
+          <t>2099.53691150171</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11.506</t>
+          <t>2093.37667576699</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>13.579</t>
+          <t>2113.1928437094</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>16.651</t>
+          <t>2149.87952274221</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>2147.31282219993</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1847.19551317237</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>1860.9457119255</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>1853.15423680889</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.221</t>
+          <t>1837.67358218241</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.257</t>
+          <t>1834.74624514354</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.398</t>
+          <t>1845.66341986478</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3.376</t>
+          <t>1867.61072480267</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.352</t>
+          <t>1881.52150147071</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.736</t>
+          <t>1904.53438861543</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.357</t>
+          <t>1928.85181902067</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>1918.39794505815</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>1926.70218406368</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>6.786</t>
+          <t>1933.90429253473</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>8.286</t>
+          <t>1958.75794578108</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>1961.21733575217</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-61.74</t>
+          <t>701304.802261108</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-58.89</t>
+          <t>776487.373711383</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>635985.074643795</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-59.3</t>
+          <t>643545.401190691</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-60.47</t>
+          <t>824736.144773895</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-60.17</t>
+          <t>1081819.67187864</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-58.43</t>
+          <t>1089314.484167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-58.72</t>
+          <t>1102602.17304957</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-55.5</t>
+          <t>1308815.13215068</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-52.49</t>
+          <t>1623206.21854965</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-52.85</t>
+          <t>2014786.55736804</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-52.36</t>
+          <t>2317531.5351085</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-47.06</t>
+          <t>2656330.43359939</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-43.88</t>
+          <t>3336283.80342492</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-43.88</t>
+          <t>2360037.21884672</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>253998779829.993</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>270571556501.922</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>207021178968.968</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>229217113100.613</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>267344007755.008</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>318267382432.902</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>341703547047.487</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>354568341480.445</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>407715974479.419</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>447041629778.831</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>467530553103.299</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>22.72</t>
+          <t>481788583496.074</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>497996487644.187</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>540019411380.627</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>461656111746.274</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>115.58</t>
+          <t>1058937.18147773</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>127.85</t>
+          <t>1116736.07292101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>132.94</t>
+          <t>1044258.26035641</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>139.61</t>
+          <t>1011695.46046075</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>143.09</t>
+          <t>1054009.48402831</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>134.69</t>
+          <t>1179943.33914034</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>140.35</t>
+          <t>1176102.18515089</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>147.46</t>
+          <t>1252329.84766961</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>125.89</t>
+          <t>1469427.2441954</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>166.19</t>
+          <t>1797530.83578138</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>159.34</t>
+          <t>2133448.93119307</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>154.99</t>
+          <t>2477531.07134706</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>160.35</t>
+          <t>3027613.30210319</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>151.61</t>
+          <t>3566779.2030106</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>177.45</t>
+          <t>2796920.48323512</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1581950.09</t>
+          <t>70541999989.7385</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1632216.323</t>
+          <t>74515191934.6909</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1661461.975</t>
+          <t>55117746541.4689</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1675206.949</t>
+          <t>58098372053.6955</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1699153.059</t>
+          <t>64889545281.624</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1763177.932</t>
+          <t>76353395005.5718</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1837303.246</t>
+          <t>82821356225.9915</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1878897.895</t>
+          <t>92944765755.6157</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1972073.419</t>
+          <t>103402566901.45</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2057200.705</t>
+          <t>115293967014.352</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2101215.075</t>
+          <t>131358963909.681</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2166673.727</t>
+          <t>143366720612.684</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2217052.892</t>
+          <t>162994548062.943</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2300250.74</t>
+          <t>172327870560.167</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2339590.627</t>
+          <t>129754681650.257</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>738866.487</t>
+          <t>-357632.379216618</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>776405.09</t>
+          <t>-340248.699209626</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>798568.775</t>
+          <t>-408273.185712613</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>803407.524</t>
+          <t>-368150.059270054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>822249.294</t>
+          <t>-229273.33925441</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>855199.877</t>
+          <t>-98123.6672616966</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>891213.742</t>
+          <t>-86787.7009838913</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>900784.444</t>
+          <t>-149727.674620044</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>941392</t>
+          <t>-160612.112044718</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>994182.907</t>
+          <t>-174324.617231727</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1014205.444</t>
+          <t>-118662.373825036</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1047826.004</t>
+          <t>-159999.536238555</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1087701.752</t>
+          <t>-371282.868503794</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1141488.884</t>
+          <t>-230495.399585683</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1160918.34</t>
+          <t>-436883.264388399</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2050739.766</t>
+          <t>183456779840.255</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2097344.068</t>
+          <t>196056364567.231</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2138286.852</t>
+          <t>151903432427.499</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2174711.948</t>
+          <t>171118741046.918</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2183529.099</t>
+          <t>202454462473.384</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2257224.744</t>
+          <t>241913987427.331</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2343784.886</t>
+          <t>258882190821.496</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2421717.544</t>
+          <t>261623575724.829</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2524777.869</t>
+          <t>304313407577.969</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2609861.024</t>
+          <t>331747662764.479</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2675242.693</t>
+          <t>336171589193.619</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2799468.074</t>
+          <t>338421862883.391</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2805198.531</t>
+          <t>335001939581.244</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2879624.773</t>
+          <t>367691540820.459</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2965900.034</t>
+          <t>331901430096.017</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>1693452.24787689</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18.201</t>
+          <t>1815616.36512757</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.497</t>
+          <t>1835440.60484036</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18.622</t>
+          <t>1710026.40859875</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>19.449</t>
+          <t>1753515.4220765</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20.438</t>
+          <t>1895478.1988017</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>1856320.04175743</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>1874128.27508539</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>2096782.94164291</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>27.651</t>
+          <t>2481700.42397383</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30.358</t>
+          <t>2938719.14606415</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>33.164</t>
+          <t>3403204.25777267</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>37.444</t>
+          <t>3942426.48415527</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>42.082</t>
+          <t>4952165.09986518</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>40.404</t>
+          <t>4395050.71325839</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1349194.712</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1376986.267</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1399861.801</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1419511.753</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1442587.813</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1500149.112</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1549300.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1599158.289</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1666535.691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1714831.804</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1751342.171</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1817422.899</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1834927.741</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1890700.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1914603.455</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11.625</t>
+          <t>1656099.77634291</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>1752367.9646248</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12.109</t>
+          <t>1775560.24831936</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12.155</t>
+          <t>1710628.53985104</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12.849</t>
+          <t>1729179.1735902</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13.583</t>
+          <t>1808311.6142287</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13.623</t>
+          <t>1805400.01718355</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14.369</t>
+          <t>1776618.243776</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16.053</t>
+          <t>1970113.47623266</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>18.169</t>
+          <t>2268914.53320351</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19.874</t>
+          <t>2608844.29810359</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>2975171.26753475</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>24.493</t>
+          <t>3462290.42564073</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>4230212.3731713</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>26.083</t>
+          <t>3950317.57228416</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>689507.836</t>
+          <t>1912553.25961093</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>686651.773</t>
+          <t>2024580.61430081</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>704610.494</t>
+          <t>2042561.38369465</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>711330.794</t>
+          <t>1955571.25946932</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>738082.053</t>
+          <t>1972638.68944014</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>785794.356</t>
+          <t>2051263.03792785</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>810353.26</t>
+          <t>2042383.82250289</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>812769.769</t>
+          <t>2011676.3093988</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>827798.036</t>
+          <t>2240887.68697854</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>825469.702</t>
+          <t>2581201.91080858</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>854710.248</t>
+          <t>2963357.73251987</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>886644.892</t>
+          <t>3375554.56705043</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>864274.694</t>
+          <t>3944366.02144599</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>895264.434</t>
+          <t>4810828.23995541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>893184.792</t>
+          <t>4486795.96693829</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>11287271.9902858</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>11942508.9348878</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>11945918.5933329</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12.94</t>
+          <t>11364521.3171774</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11407697.1526909</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>11324336.6067459</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>11034687.812736</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>10701325.7988415</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>11762000.0633527</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20.44</t>
+          <t>13123295.6721036</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>14755636.6807407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>16116254.6275372</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>18165154.8461758</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>16479061.5746225</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>15662341.9588696</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.567</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.598</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8.255</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.763</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8.758</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8.399</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.823</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7.102</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>5.713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>4.938</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5.419</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>738866487267.488</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>776405089738.155</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>798568775381.001</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>803407523986.924</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>822249294395.26</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>855199877163.474</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>891213742017.547</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>900784443795.818</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>941392000201.921</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>994182906825.701</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1014205443777.12</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1047826003582.13</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1087701752215.65</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1141488883601.7</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1160918340324.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1581950090380.27</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1632216323446.71</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1661461975045.46</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1675206949481.46</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1699153059439.56</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1763177932464.47</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1837303245908.48</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1878897894530.26</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1972073419433.81</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2057200705221.21</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2101215074715.22</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2166673727183.3</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2217052892146.03</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2300250740267.96</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2339590626746.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1349194711912.82</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1376986266558.49</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1399861801088.96</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1419511753335.98</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1442587813367.67</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1500149111844.83</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1549300099794.48</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1599158289186</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1666535691327.72</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1714831804475.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1751342171202.12</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1817422899264.31</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1834927740539.67</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1890700180462.9</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1914603455316.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>856406416.7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>877089703.9</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>896558927.5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>911591136.6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>926097036</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>955308488.8</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>983772057.8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>998605592.9</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1035462227</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1066541600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1095296771</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1124550408</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1146412933</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1174341498</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1192927772</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>370556518.425133</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>379509221.724772</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>390190196.806831</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>395691036.171245</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>400130624.103076</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>413204257.946556</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>426421156.075177</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>433847564.736811</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>450765196.188898</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>467784408.353138</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>483061497.143057</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>500543459.622823</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>514719589.10591</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>530954814.689202</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>540637734.903813</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1581950090380.27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1632216323446.71</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1661461975045.46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1675206949481.46</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1699153059439.56</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1763177932464.47</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1837303245908.48</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1878897894530.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1972073419433.81</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2057200705221.21</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2101215074715.22</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2166673727183.3</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2217052892146.03</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2300250740267.96</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2339590626746.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>738866487267.488</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>776405089738.155</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>798568775381.001</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>803407523986.924</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>822249294395.26</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>855199877163.474</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>891213742017.547</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>900784443795.818</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>941392000201.921</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>994182906825.701</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1014205443777.12</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1047826003582.13</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1087701752215.65</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1141488883601.7</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1160918340324.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228898648427933</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.231919837016752</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.233019160662987</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.235284951021892</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.240991356161571</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.247797250380012</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.249827856813299</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.256671032957441</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.249986894033455</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.274989880290778</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.282125256882255</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.287263989153529</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.289429468407217</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.297021226523762</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.306401074424642</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.453619150842876</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.458991502302581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.463130386661843</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.465589634981445</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.471018569897122</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.471636483388593</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.473224520750676</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.47349384372661</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.460707877633889</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472300993256089</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.470266756125835</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.469502423185547</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.466965109699573</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.464136590079048</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.463349681517467</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.317482200729191</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.309088660680667</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.30385045267517</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.299125413996663</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.287990073941307</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.280566266231395</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.276947622436025</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.269835123315949</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.289305228332656</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.252709126453133</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.24760798699191</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.243233587660924</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.24360542189321</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.23884218339719</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.230249244057891</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.155282646906169</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.157701180745512</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.159117651873489</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.160829657779038</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.164682133111337</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.168121531150933</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.170713780599449</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176732786541879</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.182257267892264</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.191332324721546</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.196486156235948</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.200505416481349</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.204207737261477</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.210861564497349</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.219257860870625</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.469773565988899</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.475494398270178</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.479710527481293</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.482224189295601</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.489192905849045</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.491557547666794</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.49292446743076</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.494602048512791</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.496828174229481</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.4980998533911</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.498983843039248</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.499095031787207</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.496367579988465</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.49598976431317</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.496499581531323</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.374943787104932</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.36680442098431</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.361171820645218</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.356946152925361</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.346124961039618</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.340320921182273</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.336361751969791</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.32866516494533</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.320914557878256</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.310567821887355</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.304530000724804</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.300399551731444</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.299424682750058</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.293148671189482</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.284242557598052</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6003296.72858969</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6424492.30466808</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6543783.60858558</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6264479.68287485</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>6333545.30128171</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6598368.92172176</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6585685.88599394</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6543553.25004621</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7373150.32141448</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8620444.58875593</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10018945.050815</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>11505716.776729</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>13579035.7644158</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>16651487.3993075</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15730361.8590702</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3100061.91984787</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3310373.4744688</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3370415.8176897</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3221261.55108232</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3257066.93491647</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3398413.01767922</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3375819.90928846</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3352394.52778614</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3736360.3239901</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4357033.25331906</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5050013.08052761</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5791309.48199016</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6786121.13592133</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>8285953.90396788</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7706866.58207004</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
